--- a/tests/testdata/excel/特殊文字.xlsx
+++ b/tests/testdata/excel/特殊文字.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FE5D5D6-3E5F-4AF3-A3B5-8D15A3928483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C732ADA-F7C2-4D3F-87A6-8E510197FBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{0A43F43E-AF33-484E-9EFC-2C3BA8C4814E}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{ADAE7950-5C4B-4638-86CF-035BD05B1E5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Unicode" sheetId="1" r:id="rId1"/>
@@ -696,7 +696,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48897AD8-AE55-4C7F-B1BE-4C8218D8F0B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF22F3FC-E406-43F0-8719-6D76ECC5C4FD}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1001,7 +1001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B5CD967-CC15-4AE3-8477-AE92F67BF505}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31A24439-B097-4BCF-9185-062FBEEE7988}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
